--- a/docs/data_dictionary.xlsx
+++ b/docs/data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e62e7c97e835051/Altieri/Estudos/Sistemas/Plano Carreira/Bases Hashtag - Treinamentos/11. Aula Claude/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_ADF5BE0B1262A03EE10600744D5DCE3AE7CC7620" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD31BA6-5E36-4B61-B234-197751B38D61}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_ADF5BE0B1262A03EE10600744D5DCE3AE7CC7620" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23463D1-4F7C-4E01-8B7D-8E7E3757BE60}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5760" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -1341,7 +1341,7 @@
       <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -1364,7 +1364,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -1387,7 +1387,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B22" s="5" t="s">

--- a/docs/data_dictionary.xlsx
+++ b/docs/data_dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e62e7c97e835051/Altieri/Estudos/Sistemas/Plano Carreira/Bases Hashtag - Treinamentos/11. Aula Claude/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_ADF5BE0B1262A03EE10600744D5DCE3AE7CC7620" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23463D1-4F7C-4E01-8B7D-8E7E3757BE60}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_ADF5BE0B1262A03EE10600744D5DCE3AE7CC7620" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66E298F6-7FFE-43DE-91F8-BDD74F30DFB9}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5760" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$4:$G$62</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1234,7 +1247,7 @@
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1257,7 +1270,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -1410,7 +1423,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -1431,7 +1444,7 @@
       <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -1452,7 +1465,7 @@
       <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1473,7 +1486,7 @@
       <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B26" s="5" t="s">

--- a/docs/data_dictionary.xlsx
+++ b/docs/data_dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e62e7c97e835051/Altieri/Estudos/Sistemas/Plano Carreira/Bases Hashtag - Treinamentos/11. Aula Claude/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_ADF5BE0B1262A03EE10600744D5DCE3AE7CC7620" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66E298F6-7FFE-43DE-91F8-BDD74F30DFB9}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_ADF5BE0B1262A03EE10600744D5DCE3AE7CC7620" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC90B922-2AD6-4739-84B3-EEA692A1C4E5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1291,7 +1291,7 @@
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1312,7 +1312,7 @@
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -1333,7 +1333,7 @@
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1677,7 +1677,7 @@
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="9" t="s">
         <v>99</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1700,7 +1700,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="8" t="s">
         <v>99</v>
       </c>
       <c r="B36" s="5" t="s">
@@ -1721,7 +1721,7 @@
       <c r="G36" s="6"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="9" t="s">
         <v>99</v>
       </c>
       <c r="B37" s="5" t="s">

--- a/docs/data_dictionary.xlsx
+++ b/docs/data_dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e62e7c97e835051/Altieri/Estudos/Sistemas/Plano Carreira/Bases Hashtag - Treinamentos/11. Aula Claude/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_ADF5BE0B1262A03EE10600744D5DCE3AE7CC7620" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC90B922-2AD6-4739-84B3-EEA692A1C4E5}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_ADF5BE0B1262A03EE10600744D5DCE3AE7CC7620" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55403E17-1DF6-49EC-9684-57BA0645EE13}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="-2385" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -596,7 +596,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -606,11 +606,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -665,14 +660,14 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -680,8 +675,8 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -992,13 +987,13 @@
   <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -1035,755 +1030,755 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="6"/>
+      <c r="F6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="6"/>
+      <c r="F7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="6"/>
+      <c r="F9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="6"/>
+      <c r="F12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="6"/>
+      <c r="F13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="6"/>
+      <c r="F14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="6"/>
+      <c r="F16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="6"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="6"/>
+      <c r="F18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="D19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="6"/>
+      <c r="F19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="D23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="6"/>
+      <c r="F23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="6"/>
+      <c r="F24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="D26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="6"/>
+      <c r="F26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="6" t="s">
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="D28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="6"/>
+      <c r="F28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="D29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="6"/>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="D30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="6"/>
+      <c r="F30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="D31" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="6"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="5" t="s">
+      <c r="D32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="6"/>
+      <c r="F32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="5" t="s">
+      <c r="D33" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="6"/>
+      <c r="F33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="D34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="6"/>
+      <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="D35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="6" t="s">
+      <c r="F35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="5" t="s">
+      <c r="D36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="6"/>
+      <c r="F36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="5"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="D37" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="5"/>
+    </row>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" s="6" t="s">
+      <c r="F39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1791,22 +1786,22 @@
       <c r="A40" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="5" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1814,433 +1809,433 @@
       <c r="A41" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="6"/>
+      <c r="F41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="6"/>
+      <c r="F42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="5"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G43" s="6"/>
+      <c r="G43" s="5"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="6"/>
+      <c r="G44" s="5"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G45" s="6"/>
+      <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G46" s="6"/>
+      <c r="G46" s="5"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G47" s="6"/>
+      <c r="G47" s="5"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" s="6" t="s">
+      <c r="F48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="6" t="s">
+      <c r="F49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="F50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F51" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" s="6"/>
+      <c r="F51" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G52" s="6"/>
+      <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G53" s="6"/>
+      <c r="G53" s="5"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G54" s="6"/>
+      <c r="G54" s="5"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F55" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" s="6" t="s">
+      <c r="F55" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="F56" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F57" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" s="6"/>
+      <c r="F57" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="5"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G58" s="6"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
+      <c r="G58" s="5"/>
+    </row>
+    <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" s="6" t="s">
+      <c r="F59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
+    <row r="60" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="5" t="s">
+      <c r="D60" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="F60" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="5" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2248,43 +2243,43 @@
       <c r="A61" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F61" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G61" s="6"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F61" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="5"/>
+    </row>
+    <row r="62" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G62" s="6"/>
+      <c r="G62" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
